--- a/Full roster Section.xlsx
+++ b/Full roster Section.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silva\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CF869A8-6618-4112-B792-682A11CC41EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450643CD-6FD5-48DE-94EA-BC600F1AE23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{773F372C-DF7E-4334-BF41-6DB0CC7AC205}"/>
   </bookViews>
   <sheets>
     <sheet name="BSIT1B" sheetId="1" r:id="rId1"/>
-    <sheet name="BSIT2B" sheetId="2" r:id="rId2"/>
+    <sheet name="BSIT2C" sheetId="4" r:id="rId2"/>
+    <sheet name="BSIT2B" sheetId="2" r:id="rId3"/>
+    <sheet name="BSCS1A" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="63">
   <si>
     <t>STUDENT NAME</t>
   </si>
@@ -160,6 +162,75 @@
   </si>
   <si>
     <t>24-00606</t>
+  </si>
+  <si>
+    <t>Borce, Shanthel</t>
+  </si>
+  <si>
+    <t>25-00590</t>
+  </si>
+  <si>
+    <t>BSCS1A</t>
+  </si>
+  <si>
+    <t>25-00591</t>
+  </si>
+  <si>
+    <t>25-00592</t>
+  </si>
+  <si>
+    <t>25-00593</t>
+  </si>
+  <si>
+    <t>25-00594</t>
+  </si>
+  <si>
+    <t>25-00595</t>
+  </si>
+  <si>
+    <t>25-00596</t>
+  </si>
+  <si>
+    <t>25-00597</t>
+  </si>
+  <si>
+    <t>25-00598</t>
+  </si>
+  <si>
+    <t>25-00599</t>
+  </si>
+  <si>
+    <t>25-00600</t>
+  </si>
+  <si>
+    <t>25-00601</t>
+  </si>
+  <si>
+    <t>25-00602</t>
+  </si>
+  <si>
+    <t>25-00603</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Puno, Janna Miakela</t>
+  </si>
+  <si>
+    <t>25-00790</t>
+  </si>
+  <si>
+    <t>BSIT2C</t>
+  </si>
+  <si>
+    <t>BSCS2C</t>
+  </si>
+  <si>
+    <t>Oliveres, Aerone</t>
+  </si>
+  <si>
+    <t>25-00794</t>
   </si>
 </sst>
 </file>
@@ -760,6 +831,200 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9E84F3-E99C-4646-8FE5-E472CEB4EB21}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192D3C0D-92A4-42D9-AF0F-CA33BE2906A4}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -949,4 +1214,196 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A071119C-791A-4FDF-A0FF-FB3517DBDF34}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>